--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="178">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-family-member-history.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-family-member-history.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-family-member-history.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-family-member-history.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -883,7 +887,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1848,13 +1852,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1905,7 +1909,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1922,10 +1926,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1948,13 +1952,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2005,7 +2009,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2022,10 +2026,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2048,13 +2052,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2105,7 +2109,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2122,10 +2126,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2148,13 +2152,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2205,7 +2209,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2222,10 +2226,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2248,13 +2252,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2305,7 +2309,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2322,10 +2326,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2348,13 +2352,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2405,7 +2409,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2422,10 +2426,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2448,13 +2452,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2484,10 +2488,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2505,7 +2509,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2522,10 +2526,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2548,13 +2552,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2605,7 +2609,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2622,10 +2626,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2648,13 +2652,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2705,7 +2709,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2717,15 +2721,15 @@
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2748,13 +2752,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2805,7 +2809,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2822,14 +2826,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -2848,16 +2852,16 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2895,19 +2899,19 @@
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2919,19 +2923,19 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -2944,25 +2948,25 @@
         <v>73</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>73</v>
@@ -3011,7 +3015,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3023,15 +3027,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3054,13 +3058,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3111,7 +3115,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3128,10 +3132,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3154,13 +3158,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3190,10 +3194,10 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3211,7 +3215,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3228,10 +3232,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3254,13 +3258,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3311,7 +3315,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3328,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3354,13 +3358,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3411,7 +3415,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3428,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3454,13 +3458,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3511,7 +3515,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3528,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3554,13 +3558,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3611,7 +3615,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="192">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-family-member-history.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-family-member-history.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-family-member-history.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-family-member-history.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-family-member-history.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-family-member-history.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-family-member-history.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-family-member-history.header.source</t>
+    <t>fr-lm-family-member-history.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-family-member-history.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -412,14 +454,14 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-family-member-history.statut</t>
+    <t>fr-lm-family-member-history.status</t>
   </si>
   <si>
     <t xml:space="preserve">code
 </t>
   </si>
   <si>
-    <t>Statut de l'observation</t>
+    <t>Statut de l'entrée</t>
   </si>
   <si>
     <t>Statut de l'entrée provenant du jdv FHIR https://hl7.org/fhir/R4/valueset-history-status</t>
@@ -431,7 +473,7 @@
     <t>fr-lm-family-member-history.relatedPerson</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-sujet
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-related-person
 </t>
   </si>
   <si>
@@ -874,11 +916,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.8515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="52.8515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.55859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.55859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -887,7 +929,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1652,13 +1694,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1709,7 +1751,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1726,10 +1768,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1752,13 +1794,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1809,7 +1851,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1826,10 +1868,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1852,13 +1894,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1909,7 +1951,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1926,10 +1968,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1952,7 +1994,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2052,13 +2094,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2109,7 +2151,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2126,10 +2168,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2140,7 +2182,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2152,13 +2194,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2209,13 +2251,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2226,10 +2268,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2240,7 +2282,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2252,13 +2294,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2309,13 +2351,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2326,10 +2368,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2340,7 +2382,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2352,13 +2394,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2409,13 +2451,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2426,10 +2468,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2437,7 +2479,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2452,13 +2494,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2488,10 +2530,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2509,10 +2551,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2526,10 +2568,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2552,13 +2594,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2588,10 +2630,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2609,7 +2651,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2640,7 +2682,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2652,13 +2694,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2709,27 +2751,27 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2752,13 +2794,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2809,7 +2851,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2826,21 +2868,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2852,17 +2894,15 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2890,84 +2930,80 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>73</v>
       </c>
@@ -3015,27 +3051,27 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3043,10 +3079,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3058,13 +3094,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3115,27 +3151,27 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3158,13 +3194,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3194,10 +3230,10 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3215,7 +3251,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3232,21 +3268,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3258,15 +3294,17 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>73</v>
@@ -3303,16 +3341,16 @@
         <v>73</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>168</v>
@@ -3321,53 +3359,57 @@
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>173</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>73</v>
       </c>
@@ -3415,27 +3457,27 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3443,7 +3485,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3458,13 +3500,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3515,10 +3557,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3532,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3558,13 +3600,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3594,10 +3636,10 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3615,7 +3657,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3627,6 +3669,406 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -606,6 +606,10 @@
   </si>
   <si>
     <t>fr-lm-family-member-history.condition.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Site de l'observation</t>
@@ -3900,13 +3904,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3974,10 +3978,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4003,10 +4007,10 @@
         <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4057,7 +4061,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-family-member-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
